--- a/backend/Community_Testing_Credentials.xlsx
+++ b/backend/Community_Testing_Credentials.xlsx
@@ -441,7 +441,7 @@
         <v>admin@mygate.com</v>
       </c>
       <c r="E2" t="str">
-        <v>Password@123</v>
+        <v>password</v>
       </c>
       <c r="F2" t="str">
         <v>N/A</v>

--- a/backend/Community_Testing_Credentials.xlsx
+++ b/backend/Community_Testing_Credentials.xlsx
@@ -441,7 +441,7 @@
         <v>admin@mygate.com</v>
       </c>
       <c r="E2" t="str">
-        <v>password</v>
+        <v>Test@1234</v>
       </c>
       <c r="F2" t="str">
         <v>N/A</v>
@@ -467,7 +467,7 @@
         <v>owner1@mygate.com</v>
       </c>
       <c r="E3" t="str">
-        <v>Password@123</v>
+        <v>Test@1234</v>
       </c>
       <c r="F3" t="str">
         <v>Villa A-101</v>
@@ -493,7 +493,7 @@
         <v>owner2@mygate.com</v>
       </c>
       <c r="E4" t="str">
-        <v>Password@123</v>
+        <v>Test@1234</v>
       </c>
       <c r="F4" t="str">
         <v>Villa A-102 (Leased)</v>
@@ -519,7 +519,7 @@
         <v>tenant1@mygate.com</v>
       </c>
       <c r="E5" t="str">
-        <v>Password@123</v>
+        <v>Test@1234</v>
       </c>
       <c r="F5" t="str">
         <v>Villa A-102</v>
@@ -545,7 +545,7 @@
         <v>tenant2@mygate.com</v>
       </c>
       <c r="E6" t="str">
-        <v>Password@123</v>
+        <v>Test@1234</v>
       </c>
       <c r="F6" t="str">
         <v>Villa B-201</v>
@@ -571,7 +571,7 @@
         <v>guard1@mygate.com</v>
       </c>
       <c r="E7" t="str">
-        <v>Password@123</v>
+        <v>Test@1234</v>
       </c>
       <c r="F7" t="str">
         <v>Gate Entrance</v>
